--- a/artfynd/A 50458-2024 artfynd.xlsx
+++ b/artfynd/A 50458-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121225611</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>121222429</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222659</v>
+        <v>121222525</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618707</v>
+        <v>618699</v>
       </c>
       <c r="R4" t="n">
-        <v>6662302</v>
+        <v>6662281</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ej markerade inom försöket.</t>
+          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,10 +1069,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222525</v>
+        <v>121222321</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1121,17 +1121,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618699</v>
+        <v>618709</v>
       </c>
       <c r="R5" t="n">
-        <v>6662281</v>
+        <v>6662242</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1203,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121222445</v>
+        <v>121222659</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618708</v>
+        <v>618707</v>
       </c>
       <c r="R6" t="n">
-        <v>6662255</v>
+        <v>6662302</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej markerade inom försöket.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1340,7 +1340,7 @@
         <v>121222595</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121222472</v>
+        <v>121222005</v>
       </c>
       <c r="B8" t="n">
-        <v>98071</v>
+        <v>100347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,30 +1483,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1519,19 +1519,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618702</v>
+        <v>618704</v>
       </c>
       <c r="R8" t="n">
-        <v>6662278</v>
+        <v>6662218</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1560,7 +1562,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1570,12 +1572,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
+          <t>Minst 70 plantor inom 5 m radie, vid friskt fuktstråk vid "utloppet" från en glup. På gränsen till två avverkningsanmälningar. Ingen naturvårdssnitsling runt den här större glupen.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1584,6 +1586,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1602,10 +1605,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121222321</v>
+        <v>121222445</v>
       </c>
       <c r="B9" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1654,17 +1657,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618709</v>
+        <v>618708</v>
       </c>
       <c r="R9" t="n">
-        <v>6662242</v>
+        <v>6662255</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1708,7 +1711,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1736,10 +1739,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121222005</v>
+        <v>121222472</v>
       </c>
       <c r="B10" t="n">
-        <v>100337</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1748,30 +1751,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1784,21 +1787,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618704</v>
+        <v>618702</v>
       </c>
       <c r="R10" t="n">
-        <v>6662218</v>
+        <v>6662278</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1827,7 +1828,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1837,12 +1838,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 70 plantor inom 5 m radie, vid friskt fuktstråk vid "utloppet" från en glup. På gränsen till två avverkningsanmälningar. Ingen naturvårdssnitsling runt den här större glupen.</t>
+          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1851,7 +1852,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50458-2024 artfynd.xlsx
+++ b/artfynd/A 50458-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121222429</v>
+        <v>121222525</v>
       </c>
       <c r="B3" t="n">
         <v>98081</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,7 +848,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -857,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618710</v>
+        <v>618699</v>
       </c>
       <c r="R3" t="n">
-        <v>6662232</v>
+        <v>6662281</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,7 +896,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +906,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
+          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,7 +939,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222525</v>
+        <v>121222445</v>
       </c>
       <c r="B4" t="n">
         <v>98081</v>
@@ -970,7 +974,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -991,10 +995,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618699</v>
+        <v>618708</v>
       </c>
       <c r="R4" t="n">
-        <v>6662281</v>
+        <v>6662255</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1041,7 +1045,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1073,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222321</v>
+        <v>121222429</v>
       </c>
       <c r="B5" t="n">
         <v>98081</v>
@@ -1104,7 +1108,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1112,26 +1116,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618709</v>
+        <v>618710</v>
       </c>
       <c r="R5" t="n">
-        <v>6662242</v>
+        <v>6662232</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1203,7 +1203,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121222659</v>
+        <v>121222321</v>
       </c>
       <c r="B6" t="n">
         <v>98081</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1255,17 +1255,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618707</v>
+        <v>618709</v>
       </c>
       <c r="R6" t="n">
-        <v>6662302</v>
+        <v>6662242</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ej markerade inom försöket.</t>
+          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1471,10 +1471,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121222005</v>
+        <v>121222472</v>
       </c>
       <c r="B8" t="n">
-        <v>100347</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,30 +1483,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1519,21 +1519,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618704</v>
+        <v>618702</v>
       </c>
       <c r="R8" t="n">
-        <v>6662218</v>
+        <v>6662278</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1562,7 +1560,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1572,12 +1570,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 70 plantor inom 5 m radie, vid friskt fuktstråk vid "utloppet" från en glup. På gränsen till två avverkningsanmälningar. Ingen naturvårdssnitsling runt den här större glupen.</t>
+          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,7 +1584,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1605,7 +1602,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121222445</v>
+        <v>121222659</v>
       </c>
       <c r="B9" t="n">
         <v>98081</v>
@@ -1640,7 +1637,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1661,10 +1658,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618708</v>
+        <v>618707</v>
       </c>
       <c r="R9" t="n">
-        <v>6662255</v>
+        <v>6662302</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1696,7 +1693,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1706,12 +1703,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej markerade inom försöket.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1739,10 +1736,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121222472</v>
+        <v>121222005</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>100347</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1751,30 +1748,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1787,19 +1784,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618702</v>
+        <v>618704</v>
       </c>
       <c r="R10" t="n">
-        <v>6662278</v>
+        <v>6662218</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1828,7 +1827,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1838,12 +1837,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
+          <t>Minst 70 plantor inom 5 m radie, vid friskt fuktstråk vid "utloppet" från en glup. På gränsen till två avverkningsanmälningar. Ingen naturvårdssnitsling runt den här större glupen.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1852,6 +1851,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50458-2024 artfynd.xlsx
+++ b/artfynd/A 50458-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121225611</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121222525</v>
+        <v>121222445</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618699</v>
+        <v>618708</v>
       </c>
       <c r="R3" t="n">
-        <v>6662281</v>
+        <v>6662255</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -911,7 +911,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222445</v>
+        <v>121222472</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,18 +987,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618708</v>
+        <v>618702</v>
       </c>
       <c r="R4" t="n">
-        <v>6662255</v>
+        <v>6662278</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1045,7 +1043,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1052,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1073,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222429</v>
+        <v>121222005</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>100360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1085,30 +1082,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1116,22 +1113,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618710</v>
+        <v>618704</v>
       </c>
       <c r="R5" t="n">
-        <v>6662232</v>
+        <v>6662218</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1160,7 +1161,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1170,12 +1171,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
+          <t>Minst 70 plantor inom 5 m radie, vid friskt fuktstråk vid "utloppet" från en glup. På gränsen till två avverkningsanmälningar. Ingen naturvårdssnitsling runt den här större glupen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1203,10 +1204,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121222321</v>
+        <v>121222429</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1238,7 +1239,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1246,26 +1247,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618709</v>
+        <v>618710</v>
       </c>
       <c r="R6" t="n">
-        <v>6662242</v>
+        <v>6662232</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1294,7 +1291,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,12 +1301,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1337,10 +1334,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121222595</v>
+        <v>121222321</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1372,7 +1369,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1389,17 +1386,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618701</v>
+        <v>618709</v>
       </c>
       <c r="R7" t="n">
-        <v>6662305</v>
+        <v>6662242</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1443,7 +1440,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1471,10 +1468,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121222472</v>
+        <v>121222595</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1506,7 +1503,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1519,16 +1516,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618702</v>
+        <v>618701</v>
       </c>
       <c r="R8" t="n">
-        <v>6662278</v>
+        <v>6662305</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1575,7 +1574,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
+          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1584,6 +1583,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>121222659</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121222005</v>
+        <v>121222525</v>
       </c>
       <c r="B10" t="n">
-        <v>100347</v>
+        <v>98094</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1748,30 +1748,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1788,17 +1788,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618704</v>
+        <v>618699</v>
       </c>
       <c r="R10" t="n">
-        <v>6662218</v>
+        <v>6662281</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 70 plantor inom 5 m radie, vid friskt fuktstråk vid "utloppet" från en glup. På gränsen till två avverkningsanmälningar. Ingen naturvårdssnitsling runt den här större glupen.</t>
+          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 50458-2024 artfynd.xlsx
+++ b/artfynd/A 50458-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121225611</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>121222445</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222472</v>
+        <v>121222595</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,16 +987,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618702</v>
+        <v>618701</v>
       </c>
       <c r="R4" t="n">
-        <v>6662278</v>
+        <v>6662305</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1043,7 +1045,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
+          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,6 +1054,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1073,7 +1076,7 @@
         <v>121222005</v>
       </c>
       <c r="B5" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1204,10 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121222429</v>
+        <v>121222472</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,7 +1242,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1247,19 +1250,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618710</v>
+        <v>618702</v>
       </c>
       <c r="R6" t="n">
-        <v>6662232</v>
+        <v>6662278</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1291,7 +1296,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1301,12 +1306,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
+          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,7 +1320,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1334,10 +1338,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121222321</v>
+        <v>121222659</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1369,7 +1373,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1386,17 +1390,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618709</v>
+        <v>618707</v>
       </c>
       <c r="R7" t="n">
-        <v>6662242</v>
+        <v>6662302</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1425,7 +1429,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1435,12 +1439,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej markerade inom försöket.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1468,10 +1472,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121222595</v>
+        <v>121222429</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1503,7 +1507,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1511,11 +1515,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618701</v>
+        <v>618710</v>
       </c>
       <c r="R8" t="n">
-        <v>6662305</v>
+        <v>6662232</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1602,10 +1602,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121222659</v>
+        <v>121222321</v>
       </c>
       <c r="B9" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1654,17 +1654,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618707</v>
+        <v>618709</v>
       </c>
       <c r="R9" t="n">
-        <v>6662302</v>
+        <v>6662242</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ej markerade inom försöket.</t>
+          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1739,7 +1739,7 @@
         <v>121222525</v>
       </c>
       <c r="B10" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 50458-2024 artfynd.xlsx
+++ b/artfynd/A 50458-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121225611</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121222445</v>
+        <v>121222005</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>100364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,30 +817,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -857,17 +857,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618708</v>
+        <v>618704</v>
       </c>
       <c r="R3" t="n">
-        <v>6662255</v>
+        <v>6662218</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Minst 70 plantor inom 5 m radie, vid friskt fuktstråk vid "utloppet" från en glup. På gränsen till två avverkningsanmälningar. Ingen naturvårdssnitsling runt den här större glupen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222595</v>
+        <v>121222472</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,18 +987,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618701</v>
+        <v>618702</v>
       </c>
       <c r="R4" t="n">
-        <v>6662305</v>
+        <v>6662278</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1045,7 +1043,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1052,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1073,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222005</v>
+        <v>121222525</v>
       </c>
       <c r="B5" t="n">
-        <v>100361</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1085,30 +1082,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1125,17 +1122,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618704</v>
+        <v>618699</v>
       </c>
       <c r="R5" t="n">
-        <v>6662218</v>
+        <v>6662281</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1164,7 +1161,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,12 +1171,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 70 plantor inom 5 m radie, vid friskt fuktstråk vid "utloppet" från en glup. På gränsen till två avverkningsanmälningar. Ingen naturvårdssnitsling runt den här större glupen.</t>
+          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1207,10 +1204,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121222472</v>
+        <v>121222321</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1242,7 +1239,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1255,19 +1252,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618702</v>
+        <v>618709</v>
       </c>
       <c r="R6" t="n">
-        <v>6662278</v>
+        <v>6662242</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1311,7 +1310,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
+          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1320,6 +1319,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121222659</v>
+        <v>121222429</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1381,11 +1381,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1394,10 +1390,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618707</v>
+        <v>618710</v>
       </c>
       <c r="R7" t="n">
-        <v>6662302</v>
+        <v>6662232</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1429,7 +1425,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1439,12 +1435,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ej markerade inom försöket.</t>
+          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1472,10 +1468,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121222429</v>
+        <v>121222659</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1507,7 +1503,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1515,7 +1511,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618710</v>
+        <v>618707</v>
       </c>
       <c r="R8" t="n">
-        <v>6662232</v>
+        <v>6662302</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
+          <t>Ej markerade inom försöket.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1602,10 +1602,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121222321</v>
+        <v>121222595</v>
       </c>
       <c r="B9" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1654,17 +1654,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618709</v>
+        <v>618701</v>
       </c>
       <c r="R9" t="n">
-        <v>6662242</v>
+        <v>6662305</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1736,10 +1736,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121222525</v>
+        <v>121222445</v>
       </c>
       <c r="B10" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618699</v>
+        <v>618708</v>
       </c>
       <c r="R10" t="n">
-        <v>6662281</v>
+        <v>6662255</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 50458-2024 artfynd.xlsx
+++ b/artfynd/A 50458-2024 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121222005</v>
+        <v>121222472</v>
       </c>
       <c r="B3" t="n">
-        <v>100364</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,30 +817,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,21 +853,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618704</v>
+        <v>618702</v>
       </c>
       <c r="R3" t="n">
-        <v>6662218</v>
+        <v>6662278</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -906,12 +904,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 70 plantor inom 5 m radie, vid friskt fuktstråk vid "utloppet" från en glup. På gränsen till två avverkningsanmälningar. Ingen naturvårdssnitsling runt den här större glupen.</t>
+          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,7 +918,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -939,7 +936,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222472</v>
+        <v>121222321</v>
       </c>
       <c r="B4" t="n">
         <v>98098</v>
@@ -974,7 +971,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,19 +984,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618702</v>
+        <v>618709</v>
       </c>
       <c r="R4" t="n">
-        <v>6662278</v>
+        <v>6662242</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1043,7 +1042,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
+          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,6 +1051,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1070,7 +1070,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222525</v>
+        <v>121222429</v>
       </c>
       <c r="B5" t="n">
         <v>98098</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1113,11 +1113,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1126,10 +1122,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618699</v>
+        <v>618710</v>
       </c>
       <c r="R5" t="n">
-        <v>6662281</v>
+        <v>6662232</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1161,7 +1157,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1171,12 +1167,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121222321</v>
+        <v>121222005</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>100364</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,30 +1212,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1260,10 +1256,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618709</v>
+        <v>618704</v>
       </c>
       <c r="R6" t="n">
-        <v>6662242</v>
+        <v>6662218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1295,7 +1291,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1305,12 +1301,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Minst 70 plantor inom 5 m radie, vid friskt fuktstråk vid "utloppet" från en glup. På gränsen till två avverkningsanmälningar. Ingen naturvårdssnitsling runt den här större glupen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1338,7 +1334,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121222429</v>
+        <v>121222445</v>
       </c>
       <c r="B7" t="n">
         <v>98098</v>
@@ -1373,7 +1369,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1381,7 +1377,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618710</v>
+        <v>618708</v>
       </c>
       <c r="R7" t="n">
-        <v>6662232</v>
+        <v>6662255</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1468,7 +1468,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121222659</v>
+        <v>121222595</v>
       </c>
       <c r="B8" t="n">
         <v>98098</v>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618707</v>
+        <v>618701</v>
       </c>
       <c r="R8" t="n">
-        <v>6662302</v>
+        <v>6662305</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ej markerade inom försöket.</t>
+          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1602,7 +1602,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121222595</v>
+        <v>121222659</v>
       </c>
       <c r="B9" t="n">
         <v>98098</v>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618701</v>
+        <v>618707</v>
       </c>
       <c r="R9" t="n">
-        <v>6662305</v>
+        <v>6662302</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej markerade inom försöket.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1736,7 +1736,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121222445</v>
+        <v>121222525</v>
       </c>
       <c r="B10" t="n">
         <v>98098</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618708</v>
+        <v>618699</v>
       </c>
       <c r="R10" t="n">
-        <v>6662255</v>
+        <v>6662281</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 50458-2024 artfynd.xlsx
+++ b/artfynd/A 50458-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121225611</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121222472</v>
+        <v>121222595</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,16 +853,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618702</v>
+        <v>618701</v>
       </c>
       <c r="R3" t="n">
-        <v>6662278</v>
+        <v>6662305</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -909,7 +911,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
+          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,6 +920,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -936,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222321</v>
+        <v>121222472</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -971,7 +974,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -984,21 +987,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618709</v>
+        <v>618702</v>
       </c>
       <c r="R4" t="n">
-        <v>6662242</v>
+        <v>6662278</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1042,7 +1043,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,7 +1052,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222429</v>
+        <v>121222321</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1113,22 +1113,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618710</v>
+        <v>618709</v>
       </c>
       <c r="R5" t="n">
-        <v>6662232</v>
+        <v>6662242</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1157,7 +1161,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1167,12 +1171,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
+          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1203,7 +1207,7 @@
         <v>121222005</v>
       </c>
       <c r="B6" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1334,10 +1338,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121222445</v>
+        <v>121222659</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1369,7 +1373,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1390,10 +1394,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618708</v>
+        <v>618707</v>
       </c>
       <c r="R7" t="n">
-        <v>6662255</v>
+        <v>6662302</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1425,7 +1429,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1435,12 +1439,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej markerade inom försöket.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1468,10 +1472,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121222595</v>
+        <v>121222429</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1503,7 +1507,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1511,11 +1515,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618701</v>
+        <v>618710</v>
       </c>
       <c r="R8" t="n">
-        <v>6662305</v>
+        <v>6662232</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1602,10 +1602,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121222659</v>
+        <v>121222445</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618707</v>
+        <v>618708</v>
       </c>
       <c r="R9" t="n">
-        <v>6662302</v>
+        <v>6662255</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ej markerade inom försöket.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1739,7 +1739,7 @@
         <v>121222525</v>
       </c>
       <c r="B10" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 50458-2024 artfynd.xlsx
+++ b/artfynd/A 50458-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121225611</v>
       </c>
       <c r="B2" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121222595</v>
+        <v>121222472</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,18 +853,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618701</v>
+        <v>618702</v>
       </c>
       <c r="R3" t="n">
-        <v>6662305</v>
+        <v>6662278</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -911,7 +909,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,7 +918,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -939,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222472</v>
+        <v>121222525</v>
       </c>
       <c r="B4" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -974,7 +971,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,16 +984,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618702</v>
+        <v>618699</v>
       </c>
       <c r="R4" t="n">
-        <v>6662278</v>
+        <v>6662281</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1043,7 +1042,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
+          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,6 +1051,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222321</v>
+        <v>121222445</v>
       </c>
       <c r="B5" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1122,17 +1122,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618709</v>
+        <v>618708</v>
       </c>
       <c r="R5" t="n">
-        <v>6662242</v>
+        <v>6662255</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1207,7 +1207,7 @@
         <v>121222005</v>
       </c>
       <c r="B6" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121222659</v>
+        <v>121222429</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1381,11 +1381,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1394,10 +1390,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618707</v>
+        <v>618710</v>
       </c>
       <c r="R7" t="n">
-        <v>6662302</v>
+        <v>6662232</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1429,7 +1425,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1439,12 +1435,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ej markerade inom försöket.</t>
+          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1472,10 +1468,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121222429</v>
+        <v>121222595</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1507,7 +1503,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1515,7 +1511,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618710</v>
+        <v>618701</v>
       </c>
       <c r="R8" t="n">
-        <v>6662232</v>
+        <v>6662305</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
+          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1602,10 +1602,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121222445</v>
+        <v>121222659</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618708</v>
+        <v>618707</v>
       </c>
       <c r="R9" t="n">
-        <v>6662255</v>
+        <v>6662302</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej markerade inom försöket.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1736,10 +1736,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121222525</v>
+        <v>121222321</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1788,17 +1788,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618699</v>
+        <v>618709</v>
       </c>
       <c r="R10" t="n">
-        <v>6662281</v>
+        <v>6662242</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 50458-2024 artfynd.xlsx
+++ b/artfynd/A 50458-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121222472</v>
+        <v>121222321</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,19 +853,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618702</v>
+        <v>618709</v>
       </c>
       <c r="R3" t="n">
-        <v>6662278</v>
+        <v>6662242</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -909,7 +911,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
+          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,6 +920,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -936,7 +939,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222525</v>
+        <v>121222472</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -971,7 +974,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -984,18 +987,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618699</v>
+        <v>618702</v>
       </c>
       <c r="R4" t="n">
-        <v>6662281</v>
+        <v>6662278</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1042,7 +1043,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,7 +1052,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1070,7 +1070,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222445</v>
+        <v>121222659</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618708</v>
+        <v>618707</v>
       </c>
       <c r="R5" t="n">
-        <v>6662255</v>
+        <v>6662302</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej markerade inom försöket.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,10 +1204,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121222005</v>
+        <v>121222445</v>
       </c>
       <c r="B6" t="n">
-        <v>100371</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,30 +1216,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1256,17 +1256,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618704</v>
+        <v>618708</v>
       </c>
       <c r="R6" t="n">
-        <v>6662218</v>
+        <v>6662255</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 70 plantor inom 5 m radie, vid friskt fuktstråk vid "utloppet" från en glup. På gränsen till två avverkningsanmälningar. Ingen naturvårdssnitsling runt den här större glupen.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1338,7 +1338,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121222429</v>
+        <v>121222595</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1381,7 +1381,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1390,10 +1394,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618710</v>
+        <v>618701</v>
       </c>
       <c r="R7" t="n">
-        <v>6662232</v>
+        <v>6662305</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1425,7 +1429,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1435,12 +1439,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
+          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1468,7 +1472,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121222595</v>
+        <v>121222525</v>
       </c>
       <c r="B8" t="n">
         <v>98105</v>
@@ -1503,7 +1507,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1524,10 +1528,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618701</v>
+        <v>618699</v>
       </c>
       <c r="R8" t="n">
-        <v>6662305</v>
+        <v>6662281</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1574,7 +1578,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1602,10 +1606,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121222659</v>
+        <v>121222005</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>100371</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1614,30 +1618,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1654,17 +1658,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618707</v>
+        <v>618704</v>
       </c>
       <c r="R9" t="n">
-        <v>6662302</v>
+        <v>6662218</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1693,7 +1697,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1703,12 +1707,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ej markerade inom försöket.</t>
+          <t>Minst 70 plantor inom 5 m radie, vid friskt fuktstråk vid "utloppet" från en glup. På gränsen till två avverkningsanmälningar. Ingen naturvårdssnitsling runt den här större glupen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1736,7 +1740,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121222321</v>
+        <v>121222429</v>
       </c>
       <c r="B10" t="n">
         <v>98105</v>
@@ -1771,7 +1775,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1779,26 +1783,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618709</v>
+        <v>618710</v>
       </c>
       <c r="R10" t="n">
-        <v>6662242</v>
+        <v>6662232</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 50458-2024 artfynd.xlsx
+++ b/artfynd/A 50458-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121222321</v>
+        <v>121222595</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -857,17 +857,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618709</v>
+        <v>618701</v>
       </c>
       <c r="R3" t="n">
-        <v>6662242</v>
+        <v>6662305</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,7 +939,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222472</v>
+        <v>121222659</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,16 +987,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618702</v>
+        <v>618707</v>
       </c>
       <c r="R4" t="n">
-        <v>6662278</v>
+        <v>6662302</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1028,7 +1030,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1038,12 +1040,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
+          <t>Ej markerade inom försöket.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,6 +1054,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1070,7 +1073,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222659</v>
+        <v>121222525</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1105,7 +1108,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1126,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618707</v>
+        <v>618699</v>
       </c>
       <c r="R5" t="n">
-        <v>6662302</v>
+        <v>6662281</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1161,7 +1164,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1171,12 +1174,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ej markerade inom försöket.</t>
+          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1338,7 +1341,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121222595</v>
+        <v>121222429</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1373,7 +1376,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1381,11 +1384,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1394,10 +1393,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618701</v>
+        <v>618710</v>
       </c>
       <c r="R7" t="n">
-        <v>6662305</v>
+        <v>6662232</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1429,7 +1428,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1439,12 +1438,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1472,7 +1471,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121222525</v>
+        <v>121222321</v>
       </c>
       <c r="B8" t="n">
         <v>98105</v>
@@ -1507,7 +1506,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1524,17 +1523,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618699</v>
+        <v>618709</v>
       </c>
       <c r="R8" t="n">
-        <v>6662281</v>
+        <v>6662242</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1578,7 +1577,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1606,10 +1605,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121222005</v>
+        <v>121222472</v>
       </c>
       <c r="B9" t="n">
-        <v>100371</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1618,30 +1617,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1654,21 +1653,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618704</v>
+        <v>618702</v>
       </c>
       <c r="R9" t="n">
-        <v>6662218</v>
+        <v>6662278</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1697,7 +1694,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1707,12 +1704,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 70 plantor inom 5 m radie, vid friskt fuktstråk vid "utloppet" från en glup. På gränsen till två avverkningsanmälningar. Ingen naturvårdssnitsling runt den här större glupen.</t>
+          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1721,7 +1718,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1740,10 +1736,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121222429</v>
+        <v>121222005</v>
       </c>
       <c r="B10" t="n">
-        <v>98105</v>
+        <v>100371</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1752,30 +1748,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1783,22 +1779,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618710</v>
+        <v>618704</v>
       </c>
       <c r="R10" t="n">
-        <v>6662232</v>
+        <v>6662218</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
+          <t>Minst 70 plantor inom 5 m radie, vid friskt fuktstråk vid "utloppet" från en glup. På gränsen till två avverkningsanmälningar. Ingen naturvårdssnitsling runt den här större glupen.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 50458-2024 artfynd.xlsx
+++ b/artfynd/A 50458-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121222595</v>
+        <v>121222659</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618701</v>
+        <v>618707</v>
       </c>
       <c r="R3" t="n">
-        <v>6662305</v>
+        <v>6662302</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -896,7 +896,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej markerade inom försöket.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,7 +939,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222659</v>
+        <v>121222525</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618707</v>
+        <v>618699</v>
       </c>
       <c r="R4" t="n">
-        <v>6662302</v>
+        <v>6662281</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ej markerade inom försöket.</t>
+          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,7 +1073,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222525</v>
+        <v>121222472</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1121,18 +1121,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618699</v>
+        <v>618702</v>
       </c>
       <c r="R5" t="n">
-        <v>6662281</v>
+        <v>6662278</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1179,7 +1177,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>8+15+10+8 plantor i 4 pinnmarkerade rutor. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1188,7 +1186,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1207,7 +1204,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121222445</v>
+        <v>121222429</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1242,7 +1239,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1250,11 +1247,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1263,10 +1256,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618708</v>
+        <v>618710</v>
       </c>
       <c r="R6" t="n">
-        <v>6662255</v>
+        <v>6662232</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1298,7 +1291,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1308,12 +1301,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1341,7 +1334,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121222429</v>
+        <v>121222595</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1376,7 +1369,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1384,7 +1377,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1393,10 +1390,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618710</v>
+        <v>618701</v>
       </c>
       <c r="R7" t="n">
-        <v>6662232</v>
+        <v>6662305</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1428,7 +1425,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1438,12 +1435,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
+          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1471,10 +1468,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121222321</v>
+        <v>121222005</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>100371</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,30 +1480,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1527,10 +1524,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618709</v>
+        <v>618704</v>
       </c>
       <c r="R8" t="n">
-        <v>6662242</v>
+        <v>6662218</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1562,7 +1559,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1572,12 +1569,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Minst 70 plantor inom 5 m radie, vid friskt fuktstråk vid "utloppet" från en glup. På gränsen till två avverkningsanmälningar. Ingen naturvårdssnitsling runt den här större glupen.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1605,7 +1602,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121222472</v>
+        <v>121222445</v>
       </c>
       <c r="B9" t="n">
         <v>98105</v>
@@ -1640,7 +1637,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1653,16 +1650,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618702</v>
+        <v>618708</v>
       </c>
       <c r="R9" t="n">
-        <v>6662278</v>
+        <v>6662255</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1709,7 +1708,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ingår i försök. Markerade med vit plastköpp och 4 vita plastpinnar.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1718,6 +1717,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121222005</v>
+        <v>121222321</v>
       </c>
       <c r="B10" t="n">
-        <v>100371</v>
+        <v>98105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1748,30 +1748,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618704</v>
+        <v>618709</v>
       </c>
       <c r="R10" t="n">
-        <v>6662218</v>
+        <v>6662242</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 70 plantor inom 5 m radie, vid friskt fuktstråk vid "utloppet" från en glup. På gränsen till två avverkningsanmälningar. Ingen naturvårdssnitsling runt den här större glupen.</t>
+          <t>Försöksyta. Inom hyggesfriförsök. Markerade plantor, 7+3 st. Intill block. Inom 5-20 m från fuktstråk med blåsippa längs ett stråk med mindre glupar. Ingen naturvårdssnitsling kring fuktstråk med äldre granlågor och gluparna. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 50458-2024 artfynd.xlsx
+++ b/artfynd/A 50458-2024 artfynd.xlsx
@@ -1204,7 +1204,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121222429</v>
+        <v>121222595</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1247,7 +1247,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1256,10 +1260,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618710</v>
+        <v>618701</v>
       </c>
       <c r="R6" t="n">
-        <v>6662232</v>
+        <v>6662305</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1291,7 +1295,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1301,12 +1305,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
+          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1334,7 +1338,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121222595</v>
+        <v>121222429</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1369,7 +1373,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1377,11 +1381,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618701</v>
+        <v>618710</v>
       </c>
       <c r="R7" t="n">
-        <v>6662305</v>
+        <v>6662232</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Försöksruta. Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ej försöksmarkerad klon av knärot.  5 m NV om markerad klon.</t>
         </is>
       </c>
       <c r="AD7" t="b">
